--- a/basedatos_partidas/salida/descompuestos/CT-05-03-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-03-020.xlsx
@@ -539,10 +539,10 @@
         <v>0.014</v>
       </c>
       <c r="G10" t="n">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>4.48</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.67</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="14">
@@ -776,10 +776,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>9.65</v>
+        <v>9.16</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="24">
@@ -795,7 +795,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>9.75</v>
+        <v>9.25</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-03-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-03-020.xlsx
@@ -565,10 +565,10 @@
         <v>0.09</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7.18</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="14">
@@ -776,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>9.16</v>
+        <v>9.23</v>
       </c>
       <c r="H23" t="n">
         <v>0.09</v>
@@ -795,7 +795,7 @@
       </c>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="5" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-05-03-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-05-03-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 05 Estructuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Estructura de madera</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
